--- a/data/美股_翻轉警報.xlsx
+++ b/data/美股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,9 +478,11 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.133</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>1</v>
       </c>
@@ -492,220 +494,250 @@
           <t>強賣</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>強賣</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🔴 極端內部人賣壓(4Q 買賣比 0.004) / 🟢 國會強買(3買/1賣)</t>
+          <t>🔴 內部人翻賣 (1.183 → 0.132)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>0.132</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.183</v>
+      </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>強買</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🔴 國會強賣(0買/3賣)</t>
+          <t>🟢 國會強買(6買/0賣)</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.782</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>0.762</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.762</v>
+      </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>強賣</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>強買</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>強買</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🔴 國會強賣(1買/5賣)</t>
+          <t>🔴 國會強賣(1買/6賣)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1.034</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>0.728</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.728</v>
+      </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>強賣</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>強賣</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🔴 國會強賣(1買/6賣)</t>
+          <t>🔴 國會強賣(0買/3賣)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.728</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>0.782</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.782</v>
+      </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>強賣</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>強賣</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🟢 國會強買(6買/0賣)</t>
+          <t>🔴 國會強賣(1買/5賣)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.762</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>1.034</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.034</v>
+      </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>強買</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>強賣</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>強賣</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🟢 國會強買(3買/0賣)</t>
+          <t>🔴 極端內部人賣壓(4Q 買賣比 0.014)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.762</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
+        <v>0.014</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.014</v>
+      </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>強買</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🔴 極端內部人賣壓(4Q 買賣比 0.014)</t>
+          <t>🔴 極端內部人賣壓(4Q 買賣比 0.004)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
+        <v>0.004</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.004</v>
+      </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>強買</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -724,9 +756,11 @@
       <c r="D10" t="n">
         <v>0.042</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>0.042</v>
+      </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
@@ -751,7 +785,9 @@
       <c r="D11" t="n">
         <v>1.892</v>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>1.892</v>
+      </c>
       <c r="F11" t="n">
         <v>4</v>
       </c>
@@ -763,59 +799,63 @@
           <t>強買</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>強買</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🟢 國會強買(3買/1賣)</t>
+          <t>🔴 極端內部人賣壓(4Q 買賣比 0.035)</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E12" t="inlineStr"/>
+        <v>0.035</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.035</v>
+      </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>強買</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>NTES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🔴 極端內部人賣壓(4Q 買賣比 0.035)</t>
+          <t>🔴 極端內部人賣壓(4Q 買賣比 0.0)</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="E13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -826,23 +866,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NTES</t>
+          <t>UAN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🔴 極端內部人賣壓(4Q 買賣比 0.0)</t>
+          <t>🟢 極端內部人淨買(4Q 買賣比 9.231)</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="inlineStr"/>
+        <v>9.231</v>
+      </c>
+      <c r="E14" t="n">
+        <v>9.231</v>
+      </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -853,21 +895,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UAN</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🟢 極端內部人淨買(4Q 買賣比 9.231)</t>
+          <t>🟢 極端內部人淨買(4Q 買賣比 99.0)</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>9.231</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
+        <v>99</v>
+      </c>
+      <c r="E15" t="n">
+        <v>99</v>
+      </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
@@ -880,21 +924,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🟢 極端內部人淨買(4Q 買賣比 99.0)</t>
+          <t>🔴 極端內部人賣壓(4Q 買賣比 0.0)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
-      </c>
-      <c r="E16" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
@@ -903,33 +949,6 @@
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>PDD</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>🔴 極端內部人賣壓(4Q 買賣比 0.0)</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/美股_翻轉警報.xlsx
+++ b/data/美股_翻轉警報.xlsx
@@ -481,7 +481,7 @@
         <v>0.132</v>
       </c>
       <c r="E2" t="n">
-        <v>0.133</v>
+        <v>0.132</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -503,94 +503,94 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🔴 內部人翻賣 (1.183 → 0.132)</t>
+          <t>🟢 國會強買(4買/1賣) / 🚨 內外一致加碼</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.132</v>
+        <v>2.383</v>
       </c>
       <c r="E3" t="n">
-        <v>1.183</v>
+        <v>1.892</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>強買</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>強買</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🟢 國會強買(6買/0賣)</t>
+          <t>🟢 極端內部人淨買(4Q 買賣比 43.0) / 🟢 內部人翻買 (0.0 → 43.0)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>0.762</v>
+        <v>43</v>
       </c>
       <c r="E4" t="n">
-        <v>0.762</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>強買</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>強買</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🔴 國會強賣(1買/6賣)</t>
+          <t>🔴 國會強賣(0買/3賣)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>0.728</v>
+        <v>0.782</v>
       </c>
       <c r="E5" t="n">
-        <v>0.728</v>
+        <v>0.782</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -606,65 +606,65 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🔴 國會強賣(0買/3賣)</t>
+          <t>🟢 國會強買(6買/0賣)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.782</v>
+        <v>0.762</v>
       </c>
       <c r="E6" t="n">
-        <v>0.782</v>
+        <v>0.762</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>強賣</t>
+          <t>強買</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>強賣</t>
+          <t>強買</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🔴 國會強賣(1買/5賣)</t>
+          <t>🔴 國會強賣(1買/6賣)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1.034</v>
+        <v>0.728</v>
       </c>
       <c r="E7" t="n">
-        <v>1.034</v>
+        <v>0.728</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -680,90 +680,94 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🔴 極端內部人賣壓(4Q 買賣比 0.014)</t>
+          <t>🔴 國會強賣(1買/5賣)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.014</v>
+        <v>1.008</v>
       </c>
       <c r="E8" t="n">
-        <v>0.014</v>
+        <v>1.034</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>強賣</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>強賣</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🔴 極端內部人賣壓(4Q 買賣比 0.004)</t>
+          <t>🔴 極端內部人賣壓(4Q 買賣比 0.016)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004</v>
+        <v>0.016</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004</v>
+        <v>0.974</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>強買</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🔴 極端內部人賣壓(4Q 買賣比 0.042)</t>
+          <t>🔴 極端內部人賣壓(4Q 買賣比 0.014)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>0.042</v>
+        <v>0.014</v>
       </c>
       <c r="E10" t="n">
-        <v>0.042</v>
+        <v>0.014</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -771,39 +775,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🟢 國會強買(4買/1賣)</t>
+          <t>🔴 極端內部人賣壓(4Q 買賣比 0.004)</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>1.892</v>
+        <v>0.004</v>
       </c>
       <c r="E11" t="n">
-        <v>1.892</v>
+        <v>0.004</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>強買</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>強買</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -813,14 +809,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🔴 極端內部人賣壓(4Q 買賣比 0.035)</t>
+          <t>🔴 極端內部人賣壓(4Q 買賣比 0.045)</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>0.035</v>
+        <v>0.045</v>
       </c>
       <c r="E12" t="n">
         <v>0.035</v>
@@ -866,22 +862,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UAN</t>
+          <t>NICE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🟢 極端內部人淨買(4Q 買賣比 9.231)</t>
+          <t>🟢 極端內部人淨買(4Q 買賣比 9.983)</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>9.231</v>
+        <v>9.983000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>9.231</v>
+        <v>1.835</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -895,22 +891,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>UAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🟢 極端內部人淨買(4Q 買賣比 99.0)</t>
+          <t>🟢 極端內部人淨買(4Q 買賣比 9.231)</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>99</v>
+        <v>9.231</v>
       </c>
       <c r="E15" t="n">
-        <v>99</v>
+        <v>9.231</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -924,22 +920,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🔴 極端內部人賣壓(4Q 買賣比 0.0)</t>
+          <t>🟢 極端內部人淨買(4Q 買賣比 99.0)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
